--- a/sample_import_tasks.xlsx
+++ b/sample_import_tasks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,447 +436,2619 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>ProjectID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ProjectDiscipline</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ProjectDiscipline</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Overdue</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RootCause</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Created</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Location</t>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Comments</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PRJ-TASK-001</t>
+          <t>T-1015</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HVAC Ductwork &amp; Chiller Unit Installation</t>
+          <t>PRJ001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>PRJ-STR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>120</v>
+          <t>Column Installation</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grid A5</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2/1/2024</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2/5/2024</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Building A - Level 3</t>
+          <t>2/7/2024</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Crane Breakdown</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>56</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Repaired after 1 day</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PRJ-TASK-002</t>
+          <t>T-1016</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Main Electrical Panel Wiring &amp; Transformer Load Test</t>
+          <t>PRJ001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>PRJ-INT</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Paint Finishes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5/10/2024</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5/20/2024</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>85</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Substation 2</t>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>38</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Awaiting color approval</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PRJ-TASK-003</t>
+          <t>T-1017</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Structural Steel Column Reinforcement &amp; Welding</t>
+          <t>PRJ001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Structural</t>
+          <t>PRJ-MEP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HVAC Ductwork</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3/15/2024</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3/22/2024</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3/18/2024</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>160</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Podium Deck</t>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>72</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ahead of schedule</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PRJ-TASK-004</t>
+          <t>T-1018</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plumbing Main Riser Hydrostatic Pressure Testing</t>
+          <t>PRJ001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>PRJ-ARC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>32</v>
+          <t>Curtain Wall Install</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>South Facade</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>4/1/2024</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>4/15/2024</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Core Shaft West</t>
+          <t>4/20/2024</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Design Revision</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>120</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Required engineering sign-off</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PRJ-TASK-005</t>
+          <t>T-1019</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Architectural Drywall Partition Framing &amp; Inspection</t>
+          <t>PRJ001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>PRJ-SITE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>45</v>
+          <t>Underground Utilities</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>West Yard</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>1/10/2024</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>1/25/2024</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Level 1 Executive Lounge</t>
+          <t>2/5/2024</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Weather Delay</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>90</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Heavy rains for 1 week</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRJ-TASK-006</t>
+          <t>T-1020</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Foundation Concrete Pouring &amp; Curing Audit</t>
+          <t>PRJ001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Civil</t>
+          <t>PRJ-STR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>200</v>
+          <t>Deck Pour</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>3/5/2024</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>3/8/2024</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Basement B2</t>
+          <t>3/8/2024</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>64</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Perfect weather conditions</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRJ-TASK-007</t>
+          <t>T-1021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fire Suppression Sprinkler Valve Calibration</t>
+          <t>PRJ001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>PRJ-INT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Floor Tile</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Restrooms</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4/10/2024</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4/12/2024</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4/15/2024</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Material Defect</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>50</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Mechanical Room 4</t>
+      <c r="O8" t="n">
+        <v>45</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Initial batch rejected</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRJ-TASK-008</t>
+          <t>T-1022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BEMS Automation Controller Commissioning</t>
+          <t>PRJ001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>PRJ-MEP</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Fire Alarm Wiring</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5/1/2024</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5/10/2024</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>28</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Coordinating with electrician</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T-1023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PRJ-ARC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Roof Membrane</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2/20/2024</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2/25/2024</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2/24/2024</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>80</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Completed before deadline</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T-1024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PRJ-SITE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Parking Lot Paving</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>North Lot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4/15/2024</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4/20/2024</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4/22/2024</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Asphalt Shortage</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>60</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Truck delivery delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T-1105</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PRJ-STR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Post-Tensioning</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Slab Area B2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3/1/2024</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3/5/2024</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3/3/2024</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>105</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Optimal curing conditions</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T-1106</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PRJ-INT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Elevator Interior</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Shaft 2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4/5/2024</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4/12/2024</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4/15/2024</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Vendor Delay</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>55</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Custom panels arrived late</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T-1107</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PRJ-MEP</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fire Sprinklers</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Level 7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>5/20/2024</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6/1/2024</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>78</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Coordinating with steel deck</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T-1108</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PRJ-ARC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Stone Cladding</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Entrance</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2/15/2024</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2/25/2024</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3/5/2024</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Design Change</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>115</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Revised architectural details</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T-1109</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PRJ-SITE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fencing Installation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Security Zone</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1/25/2024</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2/1/2024</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1/29/2024</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>42</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Early completion</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T-1110</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PRJ-STR</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Metal Decking</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Level 8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3/10/2024</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3/15/2024</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3/20/2024</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Crew Shortage</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>88</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Subcontractor staffing issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T-1111</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PRJ-INT</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Millwork Installation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Executive Suite</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6/5/2024</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6/15/2024</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>64</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>65</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Custom fabrication in progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T-1112</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PRJ-MEP</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Electrical Terminations</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Control Room</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4/10/2024</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4/15/2024</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4/12/2024</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>48</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Completed ahead of schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T-1113</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PRJ-ARC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Skylight Assembly</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Atrium</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3/5/2024</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3/12/2024</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3/18/2024</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Glass Breakage</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>92</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Replacement unit required</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T-1114</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PRJ-SITE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Irrigation System</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Landscape Area</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2/1/2024</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2/10/2024</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2/15/2024</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Utility Conflict</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>50</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Required water line relocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T-1001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PRJ-ARC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Foundation Pour</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>North Wing</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1/5/2024</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1/20/2024</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1/22/2024</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Weather Delay</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>120</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Concrete test passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T-1002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PRJ-STR</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Control Center</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Steel Erection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>East Tower</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2/10/2024</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3/15/2024</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>85</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Waiting for inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T-1003</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PRJ-MEP</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Electrical Rough-in</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1/15/2024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2/1/2024</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2/5/2024</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Supplier Delay</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>65</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Completed with 3 RFIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T-1004</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PRJ-INT</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Drywall Installation</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Suite 401</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3/1/2024</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3/10/2024</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3/8/2024</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>42</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Early completion</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T-1005</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PRJ-SITE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Excavation</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>West Lot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1/10/2024</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1/25/2024</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1/30/2024</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Equipment Failure</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>150</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Rock encounter required blasting</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T-1006</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PRJ-STR</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Column Installation</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grid A5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2/1/2024</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2/5/2024</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2/7/2024</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Crane Breakdown</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>56</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Repaired after 1 day</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T-1007</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PRJ-INT</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Paint Finishes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>5/10/2024</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5/20/2024</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>38</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Awaiting color approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T-1008</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PRJ-MEP</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>HVAC Ductwork</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3/15/2024</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3/22/2024</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3/18/2024</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>72</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ahead of schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T-1009</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PRJ-ARC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Curtain Wall Install</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>South Facade</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>4/1/2024</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>4/15/2024</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4/20/2024</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Design Revision</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>120</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Required engineering sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T-1010</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PRJ-SITE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Underground Utilities</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>West Yard</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1/10/2024</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1/25/2024</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2/5/2024</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>11</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Weather Delay</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>90</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Heavy rains for 1 week</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T-1196</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PRJ-INT</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Floor Tile</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Restrooms</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>4/10/2024</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>4/12/2024</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4/15/2024</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L32" t="b">
+        <v>1</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Material Defect</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>45</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Initial batch rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T-1197</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PRJ-MEP</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Fire Alarm Wiring</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>5/1/2024</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5/10/2024</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>28</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Coordinating with electrician</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T-1198</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PRJ-ARC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Roof Membrane</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Penthouse</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2/20/2024</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2/25/2024</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2/24/2024</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>80</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Completed before deadline</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T-1199</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PRJ-SITE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Parking Lot Paving</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>North Lot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>4/15/2024</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>4/20/2024</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4/22/2024</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L35" t="b">
+        <v>1</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Asphalt Shortage</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>60</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Truck delivery delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T-1200</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PRJ001</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PRJ-ARC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Glass Curtain Wall</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>North Elevation</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>6/1/2024</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6/15/2024</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>95</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sequencing with steel work</t>
         </is>
       </c>
     </row>
